--- a/doctool/test/auto/scenario07/システム機能設計書_サンプル_S07.xlsx
+++ b/doctool/test/auto/scenario07/システム機能設計書_サンプル_S07.xlsx
@@ -2252,7 +2252,9 @@
       <text>
         <t>山田　太郎:*
 実施日:2023/08/01
-開始:09:00</t>
+開始:09:00
+終了:14:00
+レビュー時間:200</t>
       </text>
     </comment>
     <comment ref="B5" authorId="0" shapeId="0">
